--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Velocity mode on 4 joints with PIDs at 100 Hz and diff_drive at 50 Hz (Compliant), but the DCC1000 encoder feedback refreshes at 20 Hz (rover_controller/README.md:57-58), so feedback is below 50 Hz. Model test tSkidSteerKinematics/testEncoderFeedbackRate fails (KnownDeviation).</t>
+          <t>Velocity mode on 4 joints with PIDs at 100 Hz and diff_drive at 50 Hz (Compliant), but the DCC1000 encoder feedback refreshes at 10 Hz (100 ms) (rover_controller/README.md:57-58), so feedback is below 50 Hz. Model test tSkidSteerKinematics/testEncoderFeedbackRate fails (KnownDeviation).</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>SWR-CRSF-001, SWR-CRSF-002, SWR-CRSF-003, SWR-CRSF-005, SWR-CTL-020, SWR-MUX-001, SWR-MUX-002, SWR-MUX-016, SWR-TRN-001, SWR-TRN-002, SWR-TRN-008</t>
+          <t>SWR-CRSF-001, SWR-CRSF-002, SWR-CRSF-003, SWR-CRSF-005, SWR-CRSF-022, SWR-CTL-020, SWR-MUX-001, SWR-MUX-002, SWR-MUX-016, SWR-TRN-006, SWR-TRN-008, SWR-TRN-023</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>SWR-BRG-006, SWR-CRSF-012, SWR-CRSF-013, SWR-DESC-009, SWR-HWI-004, SWR-HWI-005, SWR-HWI-008, SWR-HWI-009, SWR-HWI-010, SWR-HWI-011, SWR-HWI-018, SWR-HWI-024, SWR-MUX-004, SWR-MUX-010, SWR-SAF-019, SWR-TRN-016</t>
+          <t>SWR-BRG-006, SWR-CRSF-012, SWR-CRSF-013, SWR-CRSF-022, SWR-DESC-009, SWR-HWI-004, SWR-HWI-005, SWR-HWI-008, SWR-HWI-009, SWR-HWI-010, SWR-HWI-011, SWR-HWI-018, SWR-HWI-024, SWR-MUX-004, SWR-MUX-010, SWR-SAF-019, SWR-TRN-016</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Links: ExpressLRS RC (UART) and LAN/Wi-Fi websocket (foxglove_bridge 8765, rosbridge 9090). Range and latency TBD and depend on the radio hardware.</t>
+          <t>Links: ExpressLRS RC (receiver UART on the RUTX11 router, forwarded to the platform over UDP 10111) and LAN/Wi-Fi websocket (foxglove_bridge 8765, rosbridge 9090). Range and latency TBD and depend on the radio hardware.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>rover_crsf_teleop/src/infrastructure/rover_crsf_teleop_node.cpp:152-158; rover_crsf_teleop/src/application/teleop_config_validation.cpp:117-139</t>
+          <t>rover_crsf_teleop/src/infrastructure/rover_crsf_teleop_node.cpp:153-159; rover_crsf_teleop/src/application/teleop_config_validation.cpp:117-139</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_serial_driver/src/infrastructure/serial_bridge_node.cpp:81-92; rover_transport/rover_udp_driver/src/infrastructure/udp_receiver_node.cpp:74-85; rover_transport/rover_udp_driver/src/infrastructure/udp_sender_node.cpp:78-89; rover_battery/launch/rover_battery.launch.py:68; rover_led/launch/rover_led.launch.py:102</t>
+          <t>rover_transport/rover_udp_driver/src/infrastructure/udp_receiver_node.cpp:77-88; rover_transport/rover_udp_driver/src/infrastructure/udp_sender_node.cpp:78-89; rover_battery/launch/rover_battery.launch.py:68; rover_led/launch/rover_led.launch.py:102; rover_crsf_teleop/launch/rover_crsf_teleop.launch.py:119</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Partial because a failed configure (device not yet enumerated, PLC or BMS bridge not up) is never retried, so the node stays UNCONFIGURED until someone steps in. That conflicts with unattended start-up (SYS-SR-024). No test exercises the autostart path directly.</t>
+          <t>Partial because a failed configure (UDP endpoint not yet available, PLC or BMS bridge not up) is never retried, so the node stays UNCONFIGURED until someone steps in. That conflicts with unattended start-up (SYS-SR-024). No test exercises the autostart path directly.</t>
         </is>
       </c>
     </row>
@@ -3862,17 +3862,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>The rover_transport shall recover from a receive error on a UDP or serial transport, by re-arming the receive or reopening the device, and resume publishing without operator action.</t>
+          <t>The rover_transport shall recover from a receive error on a UDP transport by re-arming the receive, and resume publishing without operator action.</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_udp_driver/src/infrastructure/asio_udp_socket.cpp:166-170; rover_transport/rover_serial_driver/src/infrastructure/asio_serial_port.cpp:138-145; rover_transport/rover_serial_driver/README.md:61-63</t>
+          <t>rover_transport/rover_udp_driver/src/infrastructure/asio_udp_socket.cpp:171-175</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>On a UDP receive error (other than operation_aborted) the handler logs and returns without re-arming. On a serial read error the port is closed and never reopened, as upstream did. The README calls auto-reconnect the obvious follow-up. Recovery time is TBD because no SYS-SR sets it.</t>
+          <t>On a UDP receive error (other than operation_aborted) the handler logs and returns without re-arming. Recovery time is TBD because no SYS-SR sets it. The serial half of this requirement (reopening a UART) was dropped with rover_serial_driver.</t>
         </is>
       </c>
     </row>
@@ -3988,17 +3988,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>The rover_transport shall publish diagnostic status on /diagnostics at 1 Hz or faster for each serial and UDP transport node (device or endpoint open/closed, bytes forwarded, bytes dropped while inactive, last receive error) and for the Modbus link (connected/disconnected, current backoff), reporting ERROR when a transport has closed or the link is down.</t>
+          <t>The rover_transport shall publish diagnostic status on /diagnostics at 1 Hz or faster for each UDP transport node (endpoint open/closed, bytes forwarded, bytes dropped while inactive, datagrams rejected by the source filter, last receive error) and for the Modbus link (connected/disconnected, current backoff), reporting ERROR when a transport has closed or the link is down.</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_io_context/src/application/inbound_byte_bridge.cpp:45-48; rover_transport/rover_io_context/src/application/outbound_byte_bridge.cpp:46-54; rover_transport/rover_serial_driver/src/infrastructure/serial_bridge_node.cpp:118-155; rover_transport/rover_modbus_driver/include/rover_modbus_driver/application/modbus_discrete_io_client.hpp:83-85</t>
+          <t>rover_transport/rover_io_context/src/application/inbound_byte_bridge.cpp:45-48; rover_transport/rover_io_context/src/application/outbound_byte_bridge.cpp:46-54; rover_transport/rover_udp_driver/src/infrastructure/udp_receiver_node.cpp:110-149; rover_transport/rover_udp_driver/include/rover_udp_driver/infrastructure/asio_udp_socket.hpp:83; rover_transport/rover_modbus_driver/include/rover_modbus_driver/application/modbus_discrete_io_client.hpp:83-85</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>No transport package depends on diagnostic_updater. The byte counters and isConnected() already exist but nothing exposes them. Modbus link diagnostics could instead be published by the consumer (rover_hardware_interface); that choice is TBD.</t>
+          <t>No transport package depends on diagnostic_updater. The byte counters, rejectedDatagrams() and isConnected() already exist but nothing exposes them. Modbus link diagnostics could instead be published by the consumer (rover_hardware_interface); that choice is TBD. For the RC input, rover_crsf_teleop's 'RC UDP link' task already reports a silent datagram stream (SWR-CRSF-021).</t>
         </is>
       </c>
     </row>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Mass is a hardware property (CAD 54.35 kg, see the xlsx Mass Properties sheet). The URDF model carries 43.45 kg (SWR-DESC-012, Deviation): the simulation/model mass does not match the CAD.</t>
+          <t>Mass is a hardware property. The URDF carries the CAD assembly mass, 57.27 kg (SolidWorks re-export 2026-10-07, batteries included; SWR-DESC-012). The xlsx Mass Properties sheet still holds the 2026-09-25 snapshot (54.35 kg). Not weighed.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Dimensions. The measured footprint is 0.913 x 0.803 m (Nav 2 footprint, outside rover_ros); limit TBD.</t>
+          <t>Dimensions. The footprint is 0.923 x 0.802 m (CAD tyre outline + 0.04 m; Nav 2 footprint, outside rover_ros); limit TBD.</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Slope/terrain; TBD. Tip-over check needs track 0.615 m (URDF) and CoM height 0.270 m (CAD): atan(0.3075/0.270) = 48.7 deg sideways.</t>
+          <t>Slope/terrain; TBD. Static sideways tip-over: tyre contact half-track 0.3068 m (URDF) and CoM height 0.215 m above the ground (CAD 2026-10-07 in the URDF frame): atan(0.3068/0.215) = 55.0 deg. The xlsx Mass Properties sheet gives a CoM height of 0.270 m from an older snapshot with a different origin.</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
@@ -2732,17 +2732,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 33.445952 kg and each wheel link mass 2.5 kg (43.445952 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 36.9775 kg and each wheel link mass 5.0741 kg (57.2739 kg in total).</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>rover_description/urdf/rover_a1/base.urdf.xacro:54-59; rover_description/config/wheel_01.yaml:3; rover_description/urdf/common/wheel.urdf.xacro:70-80</t>
+          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-79; rover_description/config/wheel_01.yaml:10; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: the modelled 43.45 kg is a CAD body + nominal wheels and is not a measured value; it does not by itself verify SYS-SR-001. The survey reported a higher CAD total mass on the SYS-SR-001 source sheet (not present in the repository, TBC). Sensors and battery have no inertial links.</t>
+          <t>Mass fidelity: 57.27 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, re-exported 2026-10-07, batteries included), not a measured value; it does not by itself verify SYS-SR-001. The four DCC1000 motor controllers carry an ASSUMPTION mass (78.8 g each, not weighed). The URDF exporter ignores mass overrides, so body_link mass is the exported 37.2298 kg corrected by -0.2522 kg by hand (base.urdf.xacro comment). Sensors have no inertial links.</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The URDF inertials total 43.45 kg against 54.35 kg in CAD. Update the URDF masses from the CAD?</t>
+          <t>The URDF now matches the CAD (57.27 kg, 2026-10-07). The xlsx Mass Properties sheet (54.35 kg, CoM height 0.270 m, 2026-09-25) predates it. Re-take the sheet from the current CAD?</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Mass is a hardware property. The URDF carries the CAD assembly mass, 57.27 kg (SolidWorks re-export 2026-10-07, batteries included; SWR-DESC-012). The xlsx Mass Properties sheet still holds the 2026-09-25 snapshot (54.35 kg). Not weighed.</t>
+          <t>Mass is a hardware property. The URDF carries the CAD assembly mass, 58.72 kg (SolidWorks per-part mass properties with the mass overrides, 2026-10-08, batteries included; SWR-DESC-012): 1.28 kg under the limit. Battery 5 kg is an owner value, RUTX11 456 g a distributor spec, DCC1000 78.8 g an ASSUMPTION. The xlsx Mass Properties sheet still holds the 2026-09-25 snapshot (54.35 kg). Not weighed.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Slope/terrain; TBD. Static sideways tip-over: tyre contact half-track 0.3068 m (URDF) and CoM height 0.215 m above the ground (CAD 2026-10-07 in the URDF frame): atan(0.3068/0.215) = 55.0 deg. The xlsx Mass Properties sheet gives a CoM height of 0.270 m from an older snapshot with a different origin.</t>
+          <t>Slope/terrain; TBD. Static sideways tip-over: tyre contact half-track 0.3068 m (URDF) and CoM height 0.218 m above the ground (CAD 2026-10-08 in the URDF frame): atan(0.3068/0.218) = 54.6 deg. The xlsx Mass Properties sheet gives a CoM height of 0.270 m from an older snapshot with a different origin.</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
@@ -2732,17 +2732,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 36.9775 kg and each wheel link mass 5.0741 kg (57.2739 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 39.5373 kg and each wheel link mass 4.79607 kg (58.7216 kg in total).</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-79; rover_description/config/wheel_01.yaml:10; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
+          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-81; rover_description/config/wheel_01.yaml:10-14; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: 57.27 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, re-exported 2026-10-07, batteries included), not a measured value; it does not by itself verify SYS-SR-001. The four DCC1000 motor controllers carry an ASSUMPTION mass (78.8 g each, not weighed). The URDF exporter ignores mass overrides, so body_link mass is the exported 37.2298 kg corrected by -0.2522 kg by hand (base.urdf.xacro comment). Sensors have no inertial links.</t>
+          <t>Mass fidelity: 58.72 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.19 kg m^2) and is not used. Sensors have no inertial links.</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The URDF now matches the CAD (57.27 kg, 2026-10-07). The xlsx Mass Properties sheet (54.35 kg, CoM height 0.270 m, 2026-09-25) predates it. Re-take the sheet from the current CAD?</t>
+          <t>The URDF now matches the CAD (58.72 kg, 2026-10-08). The xlsx Mass Properties sheet (54.35 kg, CoM height 0.270 m, 2026-09-25) predates it. Re-take the sheet from the current CAD?</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Mass is a hardware property. The URDF carries the CAD assembly mass, 58.72 kg (SolidWorks per-part mass properties with the mass overrides, 2026-10-08, batteries included; SWR-DESC-012): 1.28 kg under the limit. Battery 5 kg is an owner value, RUTX11 456 g a distributor spec, DCC1000 78.8 g an ASSUMPTION. The xlsx Mass Properties sheet still holds the 2026-09-25 snapshot (54.35 kg). Not weighed.</t>
+          <t>Mass is a hardware property. The URDF carries the CAD assembly mass, 58.67 kg (SolidWorks per-part mass properties with the mass overrides, 2026-10-08, batteries included; SWR-DESC-012): 1.33 kg under the limit. Battery 5 kg is an owner value, RUTX11 456 g a distributor spec, DCC1000 78.8 g an ASSUMPTION. The xlsx Mass Properties sheet still holds the 2026-09-25 snapshot (54.35 kg). Not weighed.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 39.5373 kg and each wheel link mass 4.79607 kg (58.7216 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 39.5026 kg and each wheel link mass 4.79294 kg (58.6744 kg in total).</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: 58.72 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.19 kg m^2) and is not used. Sensors have no inertial links.</t>
+          <t>Mass fidelity: 58.67 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08 after the clash fixes, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.18 kg m^2) and is not used. Sensors have no inertial links.</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The URDF now matches the CAD (58.72 kg, 2026-10-08). The xlsx Mass Properties sheet (54.35 kg, CoM height 0.270 m, 2026-09-25) predates it. Re-take the sheet from the current CAD?</t>
+          <t>The URDF now matches the CAD (58.67 kg, 2026-10-08). The xlsx Mass Properties sheet (54.35 kg, CoM height 0.270 m, 2026-09-25) predates it. Re-take the sheet from the current CAD?</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall, in rover_load_urdf.launch.py, take the IMU, lidar and GPS mount poses from the ROVER_{IMU,LIDAR,GPS}_LOCALIZATION_{X,Y,Z} and _ORIENTATION_{R,P,Y} environment variables, falling back to the defaults (IMU xyz (-0.09, 0.0, 0.2), rpy (3.14159, 0.0, 0.0); lidar and GPS all 0.0) for unset or non-finite values.</t>
+          <t>The rover_description shall, in rover_load_urdf.launch.py, take the IMU, lidar and GPS mount poses from the ROVER_SYSTEM_MOUNT_{IMU,LIDAR,GPS}_{X,Y,Z} and _{ROLL,PITCH,YAW} environment variables, falling back to the defaults (IMU xyz (-0.09, 0.0, 0.2), rpy (3.14159, 0.0, 0.0); lidar and GPS all 0.0) for unset or non-finite values.</t>
         </is>
       </c>
     </row>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS_SYS-SR-COMPLIANCE-V-001.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The rover_battery shall publish sensor_msgs/BatteryState on rover_battery/battery_status (depth 5, reliable, volatile) once for every valid BMS frame received.</t>
+          <t>The rover_battery shall publish sensor_msgs/BatteryState on battery/battery_status (depth 5, reliable, volatile) once for every valid BMS frame received.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The rover_battery shall publish rover_battery/battery_status at 1 Hz or faster regardless of the BMS packet timing, republishing the latest reading on a fixed-rate timer, and shall enter the watchdog state (SWR-BAT-008) when the latest reading is older than [TBD] s.</t>
+          <t>The rover_battery shall publish battery/battery_status at 1 Hz or faster regardless of the BMS packet timing, republishing the latest reading on a fixed-rate timer, and shall enter the watchdog state (SWR-BAT-008) when the latest reading is older than [TBD] s.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>The rover_safety shall, in rover_safety_node, evaluate motor-driver temperature from hardware_interface/rover_driver_state and trip the software E-Stop above a driver temperature limit of [TBD] degC.</t>
+          <t>The rover_safety shall, in rover_safety_node, evaluate motor-driver temperature from hardware_interface/driver_state and trip the software E-Stop above a driver temperature limit of [TBD] degC.</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
